--- a/data/AAPL/AAPL_Financial_Analysis.xlsx
+++ b/data/AAPL/AAPL_Financial_Analysis.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentiment Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Price" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Price" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentiment Analysis" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,9 +28,9 @@
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="+0.00%;-0.00%;0.00%"/>
     <numFmt numFmtId="168" formatCode="+$#,##0.00;-$#,##0.00;&quot;$0.00&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0&quot; d&quot;"/>
-    <numFmt numFmtId="171" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0&quot; d&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,22 +302,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -339,7 +339,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -420,7 +435,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -1007,364 +1021,370 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="21" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B4" s="38" t="n"/>
+        <v>2016</v>
+      </c>
+      <c r="B4" s="54" t="n">
+        <v>28.17749977111816</v>
+      </c>
       <c r="C4" s="24" t="n"/>
-      <c r="D4" s="23" t="n"/>
+      <c r="D4" s="23" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>200</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>38</v>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="n">
+        <v>215.639</v>
+      </c>
+      <c r="G4" s="54" t="n">
+        <v>45.687</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>0.235</v>
+        <v>0.2783541010670612</v>
       </c>
       <c r="I4" s="39" t="n">
-        <v>0.4222222222222222</v>
-      </c>
-      <c r="J4" s="40" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="K4" s="40" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.3562366958026963</v>
+      </c>
+      <c r="J4" s="55" t="n">
+        <v>1.352669417512594</v>
+      </c>
+      <c r="K4" s="55" t="n">
+        <v>0.6786173771335449</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B5" s="41" t="n">
-        <v>28.17749977111816</v>
-      </c>
-      <c r="C5" s="29" t="n"/>
+        <v>2017</v>
+      </c>
+      <c r="B5" s="56" t="n">
+        <v>38.52999877929688</v>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>0.3673</v>
+      </c>
       <c r="D5" s="28" t="n">
-        <v>0.75</v>
+        <v>0.6704</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F5" s="41" t="n">
-        <v>216</v>
-      </c>
-      <c r="G5" s="41" t="n">
-        <v>41.8</v>
+      <c r="F5" s="56" t="n">
+        <v>229.234</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>48.351</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>0.2415277777777778</v>
+        <v>0.2676042820872994</v>
       </c>
       <c r="I5" s="42" t="n">
-        <v>0.4300411522633745</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>1.06265664160401</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>0.8919753086419753</v>
+        <v>0.3607018433832909</v>
+      </c>
+      <c r="J5" s="57" t="n">
+        <v>1.276062848413911</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>0.8988414511328117</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="21" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B6" s="38" t="n">
-        <v>38.52999877929688</v>
+        <v>2018</v>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>56.43500137329102</v>
       </c>
       <c r="C6" s="44" t="n">
-        <v>0.3673</v>
+        <v>0.4648</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0.6704</v>
+        <v>0.8944</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F6" s="38" t="n">
-        <v>233.28</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>45.98</v>
+      <c r="F6" s="54" t="n">
+        <v>265.595</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>59.531</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>0.2482368827160494</v>
+        <v>0.2669402661947702</v>
       </c>
       <c r="I6" s="39" t="n">
-        <v>0.4380048773052888</v>
-      </c>
-      <c r="J6" s="40" t="n">
-        <v>1.072777181047858</v>
-      </c>
-      <c r="K6" s="40" t="n">
-        <v>0.8424211248285323</v>
+        <v>0.5556011834209077</v>
+      </c>
+      <c r="J6" s="55" t="n">
+        <v>1.12384269162973</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>1.077211681148329</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="26" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B7" s="41" t="n">
-        <v>56.43500137329102</v>
-      </c>
-      <c r="C7" s="44" t="n">
-        <v>0.4648</v>
+        <v>2019</v>
+      </c>
+      <c r="B7" s="56" t="n">
+        <v>54.70500183105469</v>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>-0.0307</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>0.8944</v>
+        <v>0.6196</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F7" s="41" t="n">
-        <v>251.9424</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <v>50.578</v>
+      <c r="F7" s="56" t="n">
+        <v>260.174</v>
+      </c>
+      <c r="G7" s="56" t="n">
+        <v>55.256</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>0.2551323516803841</v>
+        <v>0.2457201718849693</v>
       </c>
       <c r="I7" s="42" t="n">
-        <v>0.4461160787368683</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>1.082994106581647</v>
-      </c>
-      <c r="K7" s="43" t="n">
-        <v>0.7956199512269471</v>
+        <v>0.6106445053487756</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>1.540125617208044</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>1.194047829546459</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="21" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B8" s="38" t="n">
-        <v>54.70500183105469</v>
-      </c>
-      <c r="C8" s="45" t="n">
-        <v>-0.0307</v>
+        <v>2020</v>
+      </c>
+      <c r="B8" s="54" t="n">
+        <v>112.2799987792969</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>1.0524</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.6196</v>
+        <v>0.5312</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F8" s="38" t="n">
-        <v>272.097792</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>55.6358</v>
+      <c r="F8" s="54" t="n">
+        <v>274.515</v>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>57.411</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>0.2622193614492836</v>
+        <v>0.2414731435440686</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>0.4543774876023658</v>
-      </c>
-      <c r="J8" s="40" t="n">
-        <v>1.093308336168139</v>
-      </c>
-      <c r="K8" s="40" t="n">
-        <v>0.75141884282545</v>
+        <v>0.8786635853012749</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>1.363604448155458</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>1.78469214404873</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="26" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B9" s="41" t="n">
-        <v>112.2799987792969</v>
+        <v>2021</v>
+      </c>
+      <c r="B9" s="56" t="n">
+        <v>146.9199981689453</v>
       </c>
       <c r="C9" s="44" t="n">
-        <v>1.0524</v>
+        <v>0.3085</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>0.5312</v>
-      </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-      <c r="F9" s="41" t="n">
-        <v>293.86561536</v>
-      </c>
-      <c r="G9" s="41" t="n">
-        <v>61.19938</v>
+        <v>1.5806</v>
+      </c>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F9" s="56" t="n">
+        <v>365.817</v>
+      </c>
+      <c r="G9" s="56" t="n">
+        <v>94.68000000000001</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>0.2695032326006526</v>
+        <v>0.2978237752756159</v>
       </c>
       <c r="I9" s="42" t="n">
-        <v>0.4627918855209281</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <v>1.103720796512597</v>
-      </c>
-      <c r="K9" s="43" t="n">
-        <v>0.7096733515573694</v>
+        <v>1.500713266761769</v>
+      </c>
+      <c r="J9" s="57" t="n">
+        <v>1.074553119595795</v>
+      </c>
+      <c r="K9" s="57" t="n">
+        <v>1.976842605801236</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="38" t="n">
-        <v>146.9199981689453</v>
+        <v>2022</v>
+      </c>
+      <c r="B10" s="54" t="n">
+        <v>150.4299926757812</v>
       </c>
       <c r="C10" s="44" t="n">
-        <v>0.3085</v>
+        <v>0.0239</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>1.5806</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>317.3748645888</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>67.319318</v>
+        <v>0.907</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+      <c r="F10" s="54" t="n">
+        <v>394.328</v>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>99.803</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>0.2769894335062358</v>
+        <v>0.3028874439552859</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.4713621056231676</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>1.114232423146007</v>
-      </c>
-      <c r="K10" s="40" t="n">
-        <v>0.6702470542486269</v>
+        <v>1.969588727502368</v>
+      </c>
+      <c r="J10" s="55" t="n">
+        <v>0.8793560286267226</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>2.369533470161036</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="26" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="41" t="n">
-        <v>150.4299926757812</v>
+        <v>2023</v>
+      </c>
+      <c r="B11" s="56" t="n">
+        <v>171.2100067138672</v>
       </c>
       <c r="C11" s="44" t="n">
-        <v>0.0239</v>
+        <v>0.1381</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>0.907</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F11" s="41" t="n">
-        <v>342.7648537559</v>
-      </c>
-      <c r="G11" s="41" t="n">
-        <v>74.05124979999999</v>
+      <c r="F11" s="56" t="n">
+        <v>383.285</v>
+      </c>
+      <c r="G11" s="56" t="n">
+        <v>96.995</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>0.28468358443696</v>
+        <v>0.2982141226502472</v>
       </c>
       <c r="I11" s="42" t="n">
-        <v>0.4800910335050681</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>1.124844160509408</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>0.6330111067903643</v>
+        <v>1.560760145463908</v>
+      </c>
+      <c r="J11" s="57" t="n">
+        <v>0.9880116717592975</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>1.787532584558942</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="38" t="n">
-        <v>171.2100067138672</v>
+        <v>2024</v>
+      </c>
+      <c r="B12" s="54" t="n">
+        <v>227.7899932861328</v>
       </c>
       <c r="C12" s="44" t="n">
-        <v>0.1381</v>
+        <v>0.3305</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.7647</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F12" s="38" t="n">
-        <v>370.18604205638</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>81.45637478</v>
+      <c r="F12" s="54" t="n">
+        <v>391.035</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>93.736</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>0.2925914617824345</v>
+        <v>0.3151022287007557</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.4889816081996146</v>
-      </c>
-      <c r="J12" s="40" t="n">
-        <v>1.135556962037985</v>
-      </c>
-      <c r="K12" s="40" t="n">
-        <v>0.5978438230797758</v>
+        <v>1.64593503072871</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>0.8673125765340832</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>1.855768217734855</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="41" t="n">
-        <v>227.7899932861328</v>
+        <v>2025</v>
+      </c>
+      <c r="B13" s="56" t="n">
+        <v>255.4600067138672</v>
       </c>
       <c r="C13" s="44" t="n">
-        <v>0.3305</v>
+        <v>0.1215</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>0.7647</v>
+        <v>0.8649</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
           <t>Cautious / Negative</t>
         </is>
       </c>
-      <c r="F13" s="41" t="n">
-        <v>399.80092542089</v>
-      </c>
-      <c r="G13" s="41" t="n">
-        <v>89.602012258</v>
+      <c r="F13" s="56" t="n">
+        <v>416.161</v>
+      </c>
+      <c r="G13" s="56" t="n">
+        <v>112.01</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>0.3007190023875017</v>
+        <v>0.3197079976259188</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>0.4980368231662731</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>1.14637179024789</v>
-      </c>
-      <c r="K13" s="43" t="n">
-        <v>0.5646302773531547</v>
+        <v>1.519129833317511</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>0.8932929222186667</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>1.229815686327696</v>
       </c>
     </row>
     <row r="16">
@@ -1394,7 +1414,7 @@
       </c>
       <c r="B18" s="49" t="inlineStr">
         <is>
-          <t>$227.79</t>
+          <t>$255.46</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1426,7 @@
       </c>
       <c r="B19" s="49" t="inlineStr">
         <is>
-          <t>+708.41%</t>
+          <t>+806.61%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1438,7 @@
       </c>
       <c r="B20" s="49" t="inlineStr">
         <is>
-          <t>+29.85%</t>
+          <t>+27.76%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1450,7 @@
       </c>
       <c r="B21" s="49" t="inlineStr">
         <is>
-          <t>0.80x</t>
+          <t>0.81x</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1462,7 @@
       </c>
       <c r="B22" s="49" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
     </row>
@@ -1501,34 +1521,34 @@
         </is>
       </c>
       <c r="C3" s="37" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D3" s="37" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E3" s="37" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F3" s="37" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G3" s="37" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H3" s="37" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="37" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="37" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="37" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1560,35 +1580,35 @@
           <t>Total Current Assets / Total Current Liabilities</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="D5" s="43" t="n">
-        <v>1.06265664160401</v>
-      </c>
-      <c r="E5" s="43" t="n">
-        <v>1.072777181047858</v>
-      </c>
-      <c r="F5" s="43" t="n">
-        <v>1.082994106581647</v>
-      </c>
-      <c r="G5" s="43" t="n">
-        <v>1.093308336168139</v>
-      </c>
-      <c r="H5" s="43" t="n">
-        <v>1.103720796512597</v>
-      </c>
-      <c r="I5" s="43" t="n">
-        <v>1.114232423146007</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>1.124844160509408</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>1.135556962037985</v>
-      </c>
-      <c r="L5" s="43" t="n">
-        <v>1.14637179024789</v>
+      <c r="C5" s="57" t="n">
+        <v>1.352669417512594</v>
+      </c>
+      <c r="D5" s="57" t="n">
+        <v>1.276062848413911</v>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>1.12384269162973</v>
+      </c>
+      <c r="F5" s="57" t="n">
+        <v>1.540125617208044</v>
+      </c>
+      <c r="G5" s="57" t="n">
+        <v>1.363604448155458</v>
+      </c>
+      <c r="H5" s="57" t="n">
+        <v>1.074553119595795</v>
+      </c>
+      <c r="I5" s="57" t="n">
+        <v>0.8793560286267226</v>
+      </c>
+      <c r="J5" s="57" t="n">
+        <v>0.9880116717592975</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>0.8673125765340832</v>
+      </c>
+      <c r="L5" s="57" t="n">
+        <v>0.8932929222186667</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1602,35 +1622,35 @@
           <t>(Cash + Mkt Securities + Accounts Rec) / Current Liab</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
-        <v>0.8105263157894737</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.8097243107769424</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>0.8089719536937582</v>
-      </c>
-      <c r="F6" s="40" t="n">
-        <v>0.8082691717957025</v>
-      </c>
-      <c r="G6" s="40" t="n">
-        <v>0.8076158968417697</v>
-      </c>
-      <c r="H6" s="40" t="n">
-        <v>0.8070120650875702</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>0.8064576172791317</v>
-      </c>
-      <c r="J6" s="40" t="n">
-        <v>0.8059524986472458</v>
-      </c>
-      <c r="K6" s="40" t="n">
-        <v>0.805496658901629</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>0.8050900522265916</v>
+      <c r="C6" s="55" t="n">
+        <v>1.049401311292813</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>0.9131172257821334</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>0.765723135899235</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>1.168041393140241</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>1.01585509336572</v>
+      </c>
+      <c r="H6" s="55" t="n">
+        <v>0.7086092715231788</v>
+      </c>
+      <c r="I6" s="55" t="n">
+        <v>0.4967333844215558</v>
+      </c>
+      <c r="J6" s="55" t="n">
+        <v>0.6266895146860462</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>0.5588745521338836</v>
+      </c>
+      <c r="L6" s="55" t="n">
+        <v>0.5703883934770665</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1644,35 +1664,35 @@
           <t>(Cash &amp; Cash Equiv + Mkt Securities) / Current Liab</t>
         </is>
       </c>
-      <c r="C7" s="43" t="n">
-        <v>0.5789473684210527</v>
-      </c>
-      <c r="D7" s="43" t="n">
-        <v>0.5759398496240602</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>0.5729609738632295</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>0.5700104683477401</v>
-      </c>
-      <c r="G7" s="43" t="n">
-        <v>0.5670880628847792</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>0.5641934898547988</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>0.5613264841870259</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>0.5584867833351821</v>
-      </c>
-      <c r="K7" s="43" t="n">
-        <v>0.5556741272532553</v>
-      </c>
-      <c r="L7" s="43" t="n">
-        <v>0.5528882583720518</v>
+      <c r="C7" s="57" t="n">
+        <v>0.8499987342733464</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>0.7358204217668181</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>0.5673249704790101</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>0.9511814449762576</v>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>0.8629023075755275</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>0.4991911125987201</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>0.3136990037796625</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>0.4236174195501968</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0.3694668692457708</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>0.3302340745391865</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1686,35 +1706,35 @@
           <t>Cash Flow from Operations / Current Liabilities</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.7649122807017544</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>0.7940517961570593</v>
-      </c>
-      <c r="F8" s="40" t="n">
-        <v>0.8243013883916139</v>
-      </c>
-      <c r="G8" s="40" t="n">
-        <v>0.8557033460446278</v>
-      </c>
-      <c r="H8" s="40" t="n">
-        <v>0.8883015687510898</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>0.9221416285129999</v>
-      </c>
-      <c r="J8" s="40" t="n">
-        <v>0.9572708334088104</v>
-      </c>
-      <c r="K8" s="40" t="n">
-        <v>0.9937382937290871</v>
-      </c>
-      <c r="L8" s="40" t="n">
-        <v>1.031594990633053</v>
+      <c r="C8" s="55" t="n">
+        <v>0.8331519125129737</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>0.6308449223322158</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>0.662587921208906</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <v>0.6563782894114532</v>
+      </c>
+      <c r="G8" s="55" t="n">
+        <v>0.7654660695308941</v>
+      </c>
+      <c r="H8" s="55" t="n">
+        <v>0.8291135709788733</v>
+      </c>
+      <c r="I8" s="55" t="n">
+        <v>0.7932810328479952</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>0.7607495802020535</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>0.6704385686425688</v>
+      </c>
+      <c r="L8" s="55" t="n">
+        <v>0.6730744848488508</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1746,35 +1766,35 @@
           <t>Total Debt (Short + Long-Term) / Stockholders' Equity</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.8919753086419753</v>
-      </c>
-      <c r="E10" s="40" t="n">
-        <v>0.8424211248285323</v>
-      </c>
-      <c r="F10" s="40" t="n">
-        <v>0.7956199512269471</v>
-      </c>
-      <c r="G10" s="40" t="n">
-        <v>0.75141884282545</v>
-      </c>
-      <c r="H10" s="40" t="n">
-        <v>0.7096733515573694</v>
-      </c>
-      <c r="I10" s="40" t="n">
-        <v>0.6702470542486269</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>0.6330111067903643</v>
-      </c>
-      <c r="K10" s="40" t="n">
-        <v>0.5978438230797758</v>
-      </c>
-      <c r="L10" s="40" t="n">
-        <v>0.5646302773531547</v>
+      <c r="C10" s="55" t="n">
+        <v>0.6786173771335449</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>0.8988414511328117</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>1.077211681148329</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>1.194047829546459</v>
+      </c>
+      <c r="G10" s="55" t="n">
+        <v>1.78469214404873</v>
+      </c>
+      <c r="H10" s="55" t="n">
+        <v>1.976842605801236</v>
+      </c>
+      <c r="I10" s="55" t="n">
+        <v>2.369533470161036</v>
+      </c>
+      <c r="J10" s="55" t="n">
+        <v>1.787532584558942</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>1.855768217734855</v>
+      </c>
+      <c r="L10" s="55" t="n">
+        <v>1.229815686327696</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1788,35 +1808,35 @@
           <t>Total Debt / Total Assets</t>
         </is>
       </c>
-      <c r="C11" s="43" t="n">
-        <v>0.2428571428571429</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>0.2336927223719676</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>0.2248741290749123</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>0.2163883128834062</v>
-      </c>
-      <c r="G11" s="43" t="n">
-        <v>0.2082227161708248</v>
-      </c>
-      <c r="H11" s="43" t="n">
-        <v>0.2003652551832465</v>
-      </c>
-      <c r="I11" s="43" t="n">
-        <v>0.1928043021574636</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>0.1855286681137866</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>0.178527586298168</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>0.1717906962491903</v>
+      <c r="C11" s="57" t="n">
+        <v>0.2705495421000603</v>
+      </c>
+      <c r="D11" s="57" t="n">
+        <v>0.3210255809058428</v>
+      </c>
+      <c r="E11" s="57" t="n">
+        <v>0.3155923166313487</v>
+      </c>
+      <c r="F11" s="57" t="n">
+        <v>0.3191784140188352</v>
+      </c>
+      <c r="G11" s="57" t="n">
+        <v>0.3600318628661759</v>
+      </c>
+      <c r="H11" s="57" t="n">
+        <v>0.3553227616936656</v>
+      </c>
+      <c r="I11" s="57" t="n">
+        <v>0.3403750478377344</v>
+      </c>
+      <c r="J11" s="57" t="n">
+        <v>0.3150690759338936</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>0.2895665515918681</v>
+      </c>
+      <c r="L11" s="57" t="n">
+        <v>0.2524155093655791</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1830,35 +1850,35 @@
           <t>Total Assets / Total Stockholders' Equity</t>
         </is>
       </c>
-      <c r="C12" s="40" t="n">
-        <v>3.888888888888889</v>
-      </c>
-      <c r="D12" s="40" t="n">
-        <v>3.816872427983539</v>
-      </c>
-      <c r="E12" s="40" t="n">
-        <v>3.746189605243103</v>
-      </c>
-      <c r="F12" s="40" t="n">
-        <v>3.676815723664527</v>
-      </c>
-      <c r="G12" s="40" t="n">
-        <v>3.608726543596666</v>
-      </c>
-      <c r="H12" s="40" t="n">
-        <v>3.541898274270801</v>
-      </c>
-      <c r="I12" s="40" t="n">
-        <v>3.476307565488009</v>
-      </c>
-      <c r="J12" s="40" t="n">
-        <v>3.411931499460408</v>
-      </c>
-      <c r="K12" s="40" t="n">
-        <v>3.348747582803738</v>
-      </c>
-      <c r="L12" s="40" t="n">
-        <v>3.286733738677749</v>
+      <c r="C12" s="55" t="n">
+        <v>2.508292462319394</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>2.799906003118309</v>
+      </c>
+      <c r="E12" s="55" t="n">
+        <v>3.413301352347709</v>
+      </c>
+      <c r="F12" s="55" t="n">
+        <v>3.74100433206613</v>
+      </c>
+      <c r="G12" s="55" t="n">
+        <v>4.957039440456695</v>
+      </c>
+      <c r="H12" s="55" t="n">
+        <v>5.563512442542399</v>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>6.961536943479634</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>5.673462491552152</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>6.408779631255487</v>
+      </c>
+      <c r="L12" s="55" t="n">
+        <v>4.872187487285204</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1872,55 +1892,35 @@
           <t>Operating Income (EBIT) / Interest Expense</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C13" s="57" t="n">
+        <v>41.22527472527472</v>
+      </c>
+      <c r="D13" s="57" t="n">
+        <v>26.40723202755058</v>
+      </c>
+      <c r="E13" s="57" t="n">
+        <v>21.8820987654321</v>
+      </c>
+      <c r="F13" s="57" t="n">
+        <v>17.87751677852349</v>
+      </c>
+      <c r="G13" s="57" t="n">
+        <v>23.07274625826662</v>
+      </c>
+      <c r="H13" s="57" t="n">
+        <v>41.19054820415879</v>
+      </c>
+      <c r="I13" s="57" t="n">
+        <v>40.74957352439441</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>29.06203915586067</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>31.19392405063291</v>
+      </c>
+      <c r="L13" s="57" t="n">
+        <v>34.82984293193717</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1952,35 +1952,35 @@
           <t>Total Revenues / Total Assets</t>
         </is>
       </c>
-      <c r="C15" s="43" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="D15" s="43" t="n">
-        <v>0.5822102425876011</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>0.5931953415043483</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>0.6043877064383926</v>
-      </c>
-      <c r="G15" s="43" t="n">
-        <v>0.6157912480693056</v>
-      </c>
-      <c r="H15" s="43" t="n">
-        <v>0.6274099508630662</v>
-      </c>
-      <c r="I15" s="43" t="n">
-        <v>0.639247874464256</v>
-      </c>
-      <c r="J15" s="43" t="n">
-        <v>0.6513091551145126</v>
-      </c>
-      <c r="K15" s="43" t="n">
-        <v>0.6635980070978299</v>
-      </c>
-      <c r="L15" s="43" t="n">
-        <v>0.6761187242128798</v>
+      <c r="C15" s="57" t="n">
+        <v>0.670340021014281</v>
+      </c>
+      <c r="D15" s="57" t="n">
+        <v>0.6107711040474902</v>
+      </c>
+      <c r="E15" s="57" t="n">
+        <v>0.7262150522933899</v>
+      </c>
+      <c r="F15" s="57" t="n">
+        <v>0.7685722388306608</v>
+      </c>
+      <c r="G15" s="57" t="n">
+        <v>0.8475615027416885</v>
+      </c>
+      <c r="H15" s="57" t="n">
+        <v>1.042207736708053</v>
+      </c>
+      <c r="I15" s="57" t="n">
+        <v>1.117852333772732</v>
+      </c>
+      <c r="J15" s="57" t="n">
+        <v>1.087077369016657</v>
+      </c>
+      <c r="K15" s="57" t="n">
+        <v>1.071387473286207</v>
+      </c>
+      <c r="L15" s="57" t="n">
+        <v>1.158445166336804</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1994,35 +1994,35 @@
           <t>Total Revenues / Accounts Receivable, Net</t>
         </is>
       </c>
-      <c r="C16" s="40" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="D16" s="40" t="n">
-        <v>9.262435677530018</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>9.437198614841904</v>
-      </c>
-      <c r="F16" s="40" t="n">
-        <v>9.615258966065337</v>
-      </c>
-      <c r="G16" s="40" t="n">
-        <v>9.796678946557135</v>
-      </c>
-      <c r="H16" s="40" t="n">
-        <v>9.98152194554878</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>10.16985254829563</v>
-      </c>
-      <c r="J16" s="40" t="n">
-        <v>10.36173655864003</v>
-      </c>
-      <c r="K16" s="40" t="n">
-        <v>10.5572410220104</v>
-      </c>
-      <c r="L16" s="40" t="n">
-        <v>10.75643424884101</v>
+      <c r="C16" s="55" t="n">
+        <v>13.68788879014853</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>12.82499720264071</v>
+      </c>
+      <c r="E16" s="55" t="n">
+        <v>11.45497282843095</v>
+      </c>
+      <c r="F16" s="55" t="n">
+        <v>11.34842536857716</v>
+      </c>
+      <c r="G16" s="55" t="n">
+        <v>17.02946650124069</v>
+      </c>
+      <c r="H16" s="55" t="n">
+        <v>13.92103660856991</v>
+      </c>
+      <c r="I16" s="55" t="n">
+        <v>13.99120068123758</v>
+      </c>
+      <c r="J16" s="55" t="n">
+        <v>12.98918937237359</v>
+      </c>
+      <c r="K16" s="55" t="n">
+        <v>11.70413049985034</v>
+      </c>
+      <c r="L16" s="55" t="n">
+        <v>10.46235261583327</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -2036,35 +2036,35 @@
           <t>(Accounts Receivable * 365) / Total Revenues</t>
         </is>
       </c>
-      <c r="C17" s="53" t="n">
-        <v>40.15</v>
-      </c>
-      <c r="D17" s="53" t="n">
-        <v>39.40648148148148</v>
-      </c>
-      <c r="E17" s="53" t="n">
-        <v>38.67673182441701</v>
-      </c>
-      <c r="F17" s="53" t="n">
-        <v>37.96049604989076</v>
-      </c>
-      <c r="G17" s="53" t="n">
-        <v>37.25752390081872</v>
-      </c>
-      <c r="H17" s="53" t="n">
-        <v>36.56756975450726</v>
-      </c>
-      <c r="I17" s="53" t="n">
-        <v>35.89039253682891</v>
-      </c>
-      <c r="J17" s="53" t="n">
-        <v>35.22575563800149</v>
-      </c>
-      <c r="K17" s="53" t="n">
-        <v>34.57342682989098</v>
-      </c>
-      <c r="L17" s="53" t="n">
-        <v>33.9331781848923</v>
+      <c r="C17" s="58" t="n">
+        <v>26.66590922792259</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <v>28.46004519399391</v>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>31.86389050998701</v>
+      </c>
+      <c r="F17" s="58" t="n">
+        <v>32.16305241876591</v>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>21.43343715279675</v>
+      </c>
+      <c r="H17" s="58" t="n">
+        <v>26.21931184171321</v>
+      </c>
+      <c r="I17" s="58" t="n">
+        <v>26.08782536365665</v>
+      </c>
+      <c r="J17" s="58" t="n">
+        <v>28.1002909062447</v>
+      </c>
+      <c r="K17" s="58" t="n">
+        <v>31.18557162402343</v>
+      </c>
+      <c r="L17" s="58" t="n">
+        <v>34.88699085209811</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -2078,35 +2078,35 @@
           <t>Cost of Goods Sold / Inventories</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n">
-        <v>30</v>
-      </c>
-      <c r="D18" s="40" t="n">
-        <v>31.16504854368932</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>32.37534169101706</v>
-      </c>
-      <c r="F18" s="40" t="n">
-        <v>33.63263651396918</v>
-      </c>
-      <c r="G18" s="40" t="n">
-        <v>34.93875832033692</v>
-      </c>
-      <c r="H18" s="40" t="n">
-        <v>36.29560330365097</v>
-      </c>
-      <c r="I18" s="40" t="n">
-        <v>37.70514129599419</v>
-      </c>
-      <c r="J18" s="40" t="n">
-        <v>39.1694186279058</v>
-      </c>
-      <c r="K18" s="40" t="n">
-        <v>40.69056109890071</v>
-      </c>
-      <c r="L18" s="40" t="n">
-        <v>42.27077706387859</v>
+      <c r="C18" s="55" t="n">
+        <v>61.62101313320826</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>29.05211122554068</v>
+      </c>
+      <c r="E18" s="55" t="n">
+        <v>41.3943377148635</v>
+      </c>
+      <c r="F18" s="55" t="n">
+        <v>39.40136385776912</v>
+      </c>
+      <c r="G18" s="55" t="n">
+        <v>41.75301649839941</v>
+      </c>
+      <c r="H18" s="55" t="n">
+        <v>32.36793313069909</v>
+      </c>
+      <c r="I18" s="55" t="n">
+        <v>45.19733117670845</v>
+      </c>
+      <c r="J18" s="55" t="n">
+        <v>33.82356657716001</v>
+      </c>
+      <c r="K18" s="55" t="n">
+        <v>28.87071095251166</v>
+      </c>
+      <c r="L18" s="55" t="n">
+        <v>38.6428821266177</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2120,35 +2120,35 @@
           <t>(Inventories * 365) / Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="C19" s="53" t="n">
-        <v>12.16666666666667</v>
-      </c>
-      <c r="D19" s="53" t="n">
-        <v>11.71183800623053</v>
-      </c>
-      <c r="E19" s="53" t="n">
-        <v>11.27401228637144</v>
-      </c>
-      <c r="F19" s="53" t="n">
-        <v>10.8525538831426</v>
-      </c>
-      <c r="G19" s="53" t="n">
-        <v>10.44685093424008</v>
-      </c>
-      <c r="H19" s="53" t="n">
-        <v>10.05631445071708</v>
-      </c>
-      <c r="I19" s="53" t="n">
-        <v>9.680377461913338</v>
-      </c>
-      <c r="J19" s="53" t="n">
-        <v>9.318494192302358</v>
-      </c>
-      <c r="K19" s="53" t="n">
-        <v>8.970139269223811</v>
-      </c>
-      <c r="L19" s="53" t="n">
-        <v>8.634806960099661</v>
+      <c r="C19" s="58" t="n">
+        <v>5.923304104250396</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <v>12.56363082071351</v>
+      </c>
+      <c r="E19" s="58" t="n">
+        <v>8.817631109699798</v>
+      </c>
+      <c r="F19" s="58" t="n">
+        <v>9.263638723714628</v>
+      </c>
+      <c r="G19" s="58" t="n">
+        <v>8.741883356235881</v>
+      </c>
+      <c r="H19" s="58" t="n">
+        <v>11.27659274770989</v>
+      </c>
+      <c r="I19" s="58" t="n">
+        <v>8.075698066617161</v>
+      </c>
+      <c r="J19" s="58" t="n">
+        <v>10.79129249032162</v>
+      </c>
+      <c r="K19" s="58" t="n">
+        <v>12.64257054841409</v>
+      </c>
+      <c r="L19" s="58" t="n">
+        <v>9.445465242577843</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -2181,34 +2181,34 @@
         </is>
       </c>
       <c r="C21" s="42" t="n">
-        <v>0.4</v>
+        <v>0.3907595564809705</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0.4037037037037037</v>
+        <v>0.384698604918991</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0.4074417009602195</v>
+        <v>0.383437188200079</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>0.4112143093024437</v>
+        <v>0.3781776810903472</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>0.4150218492033923</v>
+        <v>0.3823324772781087</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>0.4188646441034237</v>
+        <v>0.4177935962516778</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>0.4227430204377147</v>
+        <v>0.4330963056136009</v>
       </c>
       <c r="J21" s="42" t="n">
-        <v>0.4266573076640087</v>
+        <v>0.4413112957720756</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>0.4306078382905165</v>
+        <v>0.4620634981523393</v>
       </c>
       <c r="L21" s="42" t="n">
-        <v>0.4345949479042934</v>
+        <v>0.4690516410716045</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -2223,34 +2223,34 @@
         </is>
       </c>
       <c r="C22" s="39" t="n">
-        <v>0.235</v>
+        <v>0.2783541010670612</v>
       </c>
       <c r="D22" s="39" t="n">
-        <v>0.2415277777777778</v>
+        <v>0.2676042820872994</v>
       </c>
       <c r="E22" s="39" t="n">
-        <v>0.2482368827160494</v>
+        <v>0.2669402661947702</v>
       </c>
       <c r="F22" s="39" t="n">
-        <v>0.2551323516803841</v>
+        <v>0.2457201718849693</v>
       </c>
       <c r="G22" s="39" t="n">
-        <v>0.2622193614492836</v>
+        <v>0.2414731435440686</v>
       </c>
       <c r="H22" s="39" t="n">
-        <v>0.2695032326006526</v>
+        <v>0.2978237752756159</v>
       </c>
       <c r="I22" s="39" t="n">
-        <v>0.2769894335062358</v>
+        <v>0.3028874439552859</v>
       </c>
       <c r="J22" s="39" t="n">
-        <v>0.28468358443696</v>
+        <v>0.2982141226502472</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>0.2925914617824345</v>
+        <v>0.3151022287007557</v>
       </c>
       <c r="L22" s="39" t="n">
-        <v>0.3007190023875017</v>
+        <v>0.3197079976259188</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0.19</v>
+        <v>0.211867983064288</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0.1935185185185185</v>
+        <v>0.2109242084507534</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0.19710219478738</v>
+        <v>0.2241420207458725</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>0.2007522354315907</v>
+        <v>0.2123809450598446</v>
       </c>
       <c r="G23" s="42" t="n">
-        <v>0.2044698694210646</v>
+        <v>0.2091361127807224</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>0.2082563484844177</v>
+        <v>0.2588179335569424</v>
       </c>
       <c r="I23" s="42" t="n">
-        <v>0.2121129475304254</v>
+        <v>0.2530964070519973</v>
       </c>
       <c r="J23" s="42" t="n">
-        <v>0.2160409650772876</v>
+        <v>0.2530623426432028</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>0.2200417236898252</v>
+        <v>0.2397125576994387</v>
       </c>
       <c r="L23" s="42" t="n">
-        <v>0.2241165704248222</v>
+        <v>0.2691506412181824</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -2307,34 +2307,34 @@
         </is>
       </c>
       <c r="C24" s="39" t="n">
-        <v>0.1085714285714286</v>
+        <v>0.1420235882195681</v>
       </c>
       <c r="D24" s="39" t="n">
-        <v>0.1126684636118598</v>
+        <v>0.1288264116658096</v>
       </c>
       <c r="E24" s="39" t="n">
-        <v>0.1169201037481564</v>
+        <v>0.1627753093171098</v>
       </c>
       <c r="F24" s="39" t="n">
-        <v>0.1213321831348793</v>
+        <v>0.1632300984296163</v>
       </c>
       <c r="G24" s="39" t="n">
-        <v>0.1259107560833653</v>
+        <v>0.1772557180259843</v>
       </c>
       <c r="H24" s="39" t="n">
-        <v>0.1306621053695301</v>
+        <v>0.2697420527518362</v>
       </c>
       <c r="I24" s="39" t="n">
-        <v>0.1355927508551727</v>
+        <v>0.2829244092925685</v>
       </c>
       <c r="J24" s="39" t="n">
-        <v>0.1407094584346121</v>
+        <v>0.2750983456377648</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>0.1460192493189394</v>
+        <v>0.2568250315085758</v>
       </c>
       <c r="L24" s="39" t="n">
-        <v>0.1515294096705968</v>
+        <v>0.3117962593356549</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2349,34 +2349,34 @@
         </is>
       </c>
       <c r="C25" s="42" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.3562366958026963</v>
       </c>
       <c r="D25" s="42" t="n">
-        <v>0.4300411522633745</v>
+        <v>0.3607018433832909</v>
       </c>
       <c r="E25" s="42" t="n">
-        <v>0.4380048773052888</v>
+        <v>0.5556011834209077</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>0.4461160787368683</v>
+        <v>0.6106445053487756</v>
       </c>
       <c r="G25" s="42" t="n">
-        <v>0.4543774876023658</v>
+        <v>0.8786635853012749</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>0.4627918855209281</v>
+        <v>1.500713266761769</v>
       </c>
       <c r="I25" s="42" t="n">
-        <v>0.4713621056231676</v>
+        <v>1.969588727502368</v>
       </c>
       <c r="J25" s="42" t="n">
-        <v>0.4800910335050681</v>
+        <v>1.560760145463908</v>
       </c>
       <c r="K25" s="42" t="n">
-        <v>0.4889816081996146</v>
+        <v>1.64593503072871</v>
       </c>
       <c r="L25" s="42" t="n">
-        <v>0.4980368231662731</v>
+        <v>1.519129833317511</v>
       </c>
     </row>
   </sheetData>
@@ -2427,34 +2427,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -2481,34 +2481,34 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>200000000000</v>
+        <v>215639000000</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>216000000000</v>
+        <v>229234000000</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>233280000000</v>
+        <v>265595000000</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>251942400000</v>
+        <v>260174000000</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>272097792000</v>
+        <v>274515000000</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>293865615360</v>
+        <v>365817000000</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>317374864588.8</v>
+        <v>394328000000</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>342764853755.9</v>
+        <v>383285000000</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>370186042056.38</v>
+        <v>391035000000</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>399800925420.89</v>
+        <v>416161000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -2518,34 +2518,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>120000000000</v>
+        <v>131376000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>128400000000</v>
+        <v>141048000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>137388000000</v>
+        <v>163756000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>147005160000</v>
+        <v>161782000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>157295521200</v>
+        <v>169559000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>168306207684</v>
+        <v>212981000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>180087642221.88</v>
+        <v>223546000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>192693777177.41</v>
+        <v>214137000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>206182341579.83</v>
+        <v>210352000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>220615105490.42</v>
+        <v>220960000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -2555,34 +2555,34 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80000000000</v>
+        <v>84263000000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>87200000000</v>
+        <v>88186000000</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>95048000000</v>
+        <v>101839000000</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>103602320000</v>
+        <v>98392000000</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>112926528800</v>
+        <v>104956000000</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>123089916392</v>
+        <v>152836000000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>134168008867.28</v>
+        <v>170782000000</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>146243129665.34</v>
+        <v>169148000000</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>159405011335.22</v>
+        <v>180683000000</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>173751462355.38</v>
+        <v>195201000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -2609,34 +2609,34 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>15000000000</v>
+        <v>10045000000</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>16500000000</v>
+        <v>11581000000</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>18150000000</v>
+        <v>14236000000</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>19965000000</v>
+        <v>16217000000</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21961500000</v>
+        <v>18752000000</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>24157650000</v>
+        <v>21914000000</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>26573415000</v>
+        <v>26251000000</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>29230756500</v>
+        <v>29915000000</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>32153832150</v>
+        <v>31370000000</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>35369215365</v>
+        <v>34550000000</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -2646,34 +2646,34 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>18000000000</v>
+        <v>14194000000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>18900000000</v>
+        <v>15261000000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>19845000000</v>
+        <v>16705000000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>20837250000</v>
+        <v>18245000000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>21879112500</v>
+        <v>19916000000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>22973068125</v>
+        <v>21973000000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>24121721531.25</v>
+        <v>25094000000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>25327807607.81</v>
+        <v>24932000000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>26594197988.2</v>
+        <v>25330000000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>27923907887.61</v>
+        <v>27601000000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -2683,34 +2683,34 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>33000000000</v>
+        <v>24239000000</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>35310000000</v>
+        <v>26842000000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>37781700000</v>
+        <v>30941000000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>40426419000</v>
+        <v>34462000000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>43256268330</v>
+        <v>38668000000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>46284207113.1</v>
+        <v>43887000000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>49524101611.02</v>
+        <v>51345000000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>52990788723.79</v>
+        <v>54847000000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>56700143934.45</v>
+        <v>56700000000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>60669154009.87</v>
+        <v>62151000000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -2720,34 +2720,34 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>47000000000</v>
+        <v>60024000000</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>52170000000</v>
+        <v>61344000000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>57908700000</v>
+        <v>70898000000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>64278657000</v>
+        <v>63930000000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>71349309270</v>
+        <v>66288000000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>79197733289.7</v>
+        <v>108949000000</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>87909483951.57001</v>
+        <v>119437000000</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>97579527186.24001</v>
+        <v>114301000000</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>108313275176.73</v>
+        <v>123216000000</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>120227735446.17</v>
+        <v>133050000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -2773,16 +2773,36 @@
           <t xml:space="preserve">    Total Non-Operating Income / (Expense)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>1348000000</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2745000000</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>2005000000</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1807000000</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>803000000</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>-334000000</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>-565000000</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>269000000</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>-321000000</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -2790,16 +2810,36 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>1456000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2323000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>3240000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>3576000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2873000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>2645000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>2931000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>3933000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>3950000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>3820000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -2807,16 +2847,36 @@
           <t xml:space="preserve">    Income Before Income Taxes</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
+      <c r="B16" s="13" t="n">
+        <v>61372000000</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>64089000000</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>72903000000</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>65737000000</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>67091000000</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>109207000000</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>119103000000</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>113736000000</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>123485000000</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>132729000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -2824,16 +2884,36 @@
           <t xml:space="preserve">    Income Tax Expense / (Benefit)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>15685000000</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>15738000000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>13372000000</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>10481000000</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>9680000000</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>14527000000</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>19300000000</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>16741000000</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>29749000000</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>20719000000</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
@@ -2842,34 +2922,34 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>38000000000</v>
+        <v>45687000000</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>41800000000</v>
+        <v>48351000000</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>45980000000</v>
+        <v>59531000000</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>50578000000</v>
+        <v>55256000000</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>55635800000</v>
+        <v>57411000000</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>61199380000</v>
+        <v>94680000000</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>67319318000</v>
+        <v>99803000000</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>74051249800</v>
+        <v>96995000000</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>81456374780</v>
+        <v>93736000000</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>89602012258</v>
+        <v>112010000000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2895,16 +2975,36 @@
           <t xml:space="preserve">    Basic Earnings Per Share (USD)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
+      <c r="B20" s="16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -2913,34 +3013,34 @@
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>3.51</v>
+        <v>2.97</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>3.93</v>
+        <v>3.28</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>4.41</v>
+        <v>5.61</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>4.93</v>
+        <v>6.11</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>5.53</v>
+        <v>6.13</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>6.19</v>
+        <v>6.08</v>
       </c>
       <c r="K21" s="17" t="n">
-        <v>6.93</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -2949,16 +3049,36 @@
           <t xml:space="preserve">    Weighted Average Shares (Basic)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>21883000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>20869000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>19822000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>18471000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>17352000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>16701000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>16216000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>15744000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>15344000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>14915000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2967,34 +3087,34 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>16000000000</v>
+        <v>22001000000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>15680000000</v>
+        <v>21006000000</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>15366400000</v>
+        <v>20001000000</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>15059072000</v>
+        <v>18596000000</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>14757890560</v>
+        <v>17528000000</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>14462732748.8</v>
+        <v>16865000000</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>14173478093.82</v>
+        <v>16326000000</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>13890008531.95</v>
+        <v>15813000000</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>13612208361.31</v>
+        <v>15408000000</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>13339964194.08</v>
+        <v>15015000000</v>
       </c>
     </row>
   </sheetData>
@@ -3045,34 +3165,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -3099,34 +3219,34 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>30000000000</v>
+        <v>20484000000</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>31200000000</v>
+        <v>20289000000</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>32448000000</v>
+        <v>25913000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>33745920000</v>
+        <v>48844000000</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>35095756800</v>
+        <v>38016000000</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>36499587072</v>
+        <v>34940000000</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>37959570554.88</v>
+        <v>23646000000</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>39477953377.08</v>
+        <v>29965000000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>41057071512.16</v>
+        <v>29943000000</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>42699354372.64</v>
+        <v>35934000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -3136,34 +3256,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>25000000000</v>
+        <v>46671000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>26250000000</v>
+        <v>53892000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>27562500000</v>
+        <v>40388000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>28940625000</v>
+        <v>51713000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>30387656250</v>
+        <v>52927000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>31907039062.5</v>
+        <v>27699000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>33502391015.63</v>
+        <v>24658000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>35177510566.41</v>
+        <v>31590000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>36936386094.73</v>
+        <v>35228000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>38783205399.46</v>
+        <v>18763000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -3173,34 +3293,34 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>22000000000</v>
+        <v>15754000000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>23320000000</v>
+        <v>17874000000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>24719200000</v>
+        <v>23186000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>26202352000</v>
+        <v>22926000000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>27774493120</v>
+        <v>16120000000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>29440962707.2</v>
+        <v>26278000000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>31207420469.63</v>
+        <v>28184000000</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>33079865697.81</v>
+        <v>29508000000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>35064657639.68</v>
+        <v>33410000000</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>37168537098.06</v>
+        <v>39777000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -3210,34 +3330,34 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>4000000000</v>
+        <v>2132000000</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>4120000000</v>
+        <v>4855000000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>4243600000</v>
+        <v>3956000000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4370908000</v>
+        <v>4106000000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>4502035240</v>
+        <v>4061000000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4637096297.2</v>
+        <v>6580000000</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4776209186.12</v>
+        <v>4946000000</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>4919495461.7</v>
+        <v>6331000000</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>5067080325.55</v>
+        <v>7286000000</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>5219092735.32</v>
+        <v>5718000000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -3246,16 +3366,36 @@
           <t xml:space="preserve">    Other Current Assets</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>21828000000</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>31735000000</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>37896000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>35230000000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>32589000000</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>39339000000</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>33971000000</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>46172000000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>47120000000</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>47765000000</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -3264,34 +3404,34 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>100000000000</v>
+        <v>106869000000</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>106000000000</v>
+        <v>128645000000</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>112360000000</v>
+        <v>131339000000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>119101600000</v>
+        <v>162819000000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>126247696000</v>
+        <v>143713000000</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>133822557760</v>
+        <v>134836000000</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>141851911225.6</v>
+        <v>135405000000</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>150363025899.14</v>
+        <v>143566000000</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>159384807453.08</v>
+        <v>152987000000</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>168947895900.27</v>
+        <v>147957000000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -3318,34 +3458,34 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>45000000000</v>
+        <v>27010000000</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>47250000000</v>
+        <v>33783000000</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>49612500000</v>
+        <v>41304000000</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>52093125000</v>
+        <v>37378000000</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>54697781250</v>
+        <v>36766000000</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>57432670312.5</v>
+        <v>39440000000</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>60304303828.13</v>
+        <v>42117000000</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>63319519019.53</v>
+        <v>43715000000</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>66485494970.51</v>
+        <v>45680000000</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>69809769719.03</v>
+        <v>49834000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -3354,16 +3494,36 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>5414000000</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>5717000000</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -3371,16 +3531,36 @@
           <t xml:space="preserve">    Intangible Assets, Net</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>3206000000</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2298000000</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -3388,16 +3568,36 @@
           <t xml:space="preserve">    Marketable Securities (Non-Current)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>170430000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>194714000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>170799000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>105341000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>100887000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>127877000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>120805000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>100544000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>109558000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>77723000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -3405,16 +3605,36 @@
           <t xml:space="preserve">    Other Non-Current Assets</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>8757000000</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>10162000000</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>22283000000</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>32978000000</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>42522000000</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>48849000000</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>54428000000</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>64758000000</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>56755000000</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>83727000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -3423,34 +3643,34 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>350000000000</v>
+        <v>321686000000</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>371000000000</v>
+        <v>375319000000</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>393260000000</v>
+        <v>365725000000</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>416855600000</v>
+        <v>338516000000</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>441866936000</v>
+        <v>323888000000</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>468378952160</v>
+        <v>351002000000</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>496481689289.6</v>
+        <v>352755000000</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>526270590646.98</v>
+        <v>352583000000</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>557846826085.79</v>
+        <v>364980000000</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>591317635650.9399</v>
+        <v>359241000000</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -3477,34 +3697,34 @@
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>40000000000</v>
+        <v>37294000000</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>42000000000</v>
+        <v>44242000000</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>44100000000</v>
+        <v>55888000000</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>46305000000</v>
+        <v>46236000000</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>48620250000</v>
+        <v>42296000000</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>51051262500</v>
+        <v>54763000000</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>53603825625</v>
+        <v>64115000000</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>56284016906.25</v>
+        <v>62611000000</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>59098217751.56</v>
+        <v>68960000000</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>62053128639.14</v>
+        <v>69860000000</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -3513,16 +3733,36 @@
           <t xml:space="preserve">    Accrued Liabilities</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>22027000000</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>25744000000</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>33327000000</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>37720000000</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>38510000000</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>47493000000</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>60845000000</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>58829000000</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>79247000000</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>75231000000</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -3530,16 +3770,36 @@
           <t xml:space="preserve">    Deferred Revenue (Current)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>8080000000</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>7548000000</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>5966000000</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>5522000000</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>6643000000</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>7612000000</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>7912000000</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>8061000000</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>8249000000</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>8190000000</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -3547,16 +3807,36 @@
           <t xml:space="preserve">    Commercial Paper and Short-Term Debt</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>11605000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>23280000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>21685000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>16240000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>17943000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>15613000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>21110000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>15807000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>19936000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>12350000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -3565,34 +3845,34 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>95000000000</v>
+        <v>79006000000</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>99750000000</v>
+        <v>100814000000</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>104737500000</v>
+        <v>116866000000</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>109974375000</v>
+        <v>105718000000</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>115473093750</v>
+        <v>105392000000</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>121246748437.5</v>
+        <v>125481000000</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>127309085859.38</v>
+        <v>153982000000</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>133674540152.34</v>
+        <v>145308000000</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>140358267159.96</v>
+        <v>176392000000</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>147376180517.96</v>
+        <v>165631000000</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -3619,34 +3899,34 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>85000000000</v>
+        <v>75427000000</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>86700000000</v>
+        <v>97207000000</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>88434000000</v>
+        <v>93735000000</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>90202680000</v>
+        <v>91807000000</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>92006733600</v>
+        <v>98667000000</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>93846868272</v>
+        <v>109106000000</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>95723805637.44</v>
+        <v>98959000000</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>97638281750.19</v>
+        <v>95281000000</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>99591047385.19</v>
+        <v>85750000000</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>101582868332.9</v>
+        <v>78328000000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -3655,16 +3935,36 @@
           <t xml:space="preserve">    Deferred Revenue (Non-Current)</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>2930000000</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2797000000</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2930000000</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>2625000000</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>3514000000</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>4330000000</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>3713000000</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>4027000000</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>4547000000</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>4210000000</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -3672,16 +3972,36 @@
           <t xml:space="preserve">    Other Non-Current Liabilities</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>36074000000</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>40454000000</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>45047000000</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>47878000000</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>50990000000</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>48995000000</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>49142000000</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>45821000000</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>41341000000</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>37339000000</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -3690,34 +4010,34 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>260000000000</v>
+        <v>193437000000</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>270400000000</v>
+        <v>241272000000</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>281216000000</v>
+        <v>258578000000</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>292464640000</v>
+        <v>248028000000</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>304163225600</v>
+        <v>258549000000</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>316329754624</v>
+        <v>287912000000</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>328982944808.96</v>
+        <v>302083000000</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>342142262601.32</v>
+        <v>290437000000</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>355827953105.37</v>
+        <v>308030000000</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>370061071229.59</v>
+        <v>285508000000</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -3744,34 +4064,34 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>50000000000</v>
+        <v>31251000000</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>51500000000</v>
+        <v>35867000000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>53045000000</v>
+        <v>40201000000</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>54636350000</v>
+        <v>45174000000</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>56275440500</v>
+        <v>50779000000</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>57963703715</v>
+        <v>57365000000</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>59702614826.45</v>
+        <v>64849000000</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>61493693271.24</v>
+        <v>73812000000</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>63338504069.38</v>
+        <v>83274000000</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>65238659191.46</v>
+        <v>93568000000</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -3780,16 +4100,36 @@
           <t xml:space="preserve">    Additional Paid-in Capital</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -3797,16 +4137,36 @@
           <t xml:space="preserve">    Retained Earnings / (Accumulated Deficit)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>96364000000</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>98330000000</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>70400000000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>45898000000</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>14966000000</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>5562000000</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>-3068000000</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>-214000000</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>-19154000000</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>-14264000000</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -3814,16 +4174,36 @@
           <t xml:space="preserve">    Accumulated Other Comprehensive Income / (Loss)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>634000000</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>-150000000</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>-3454000000</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>-584000000</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>-406000000</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>163000000</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>-11109000000</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>-11452000000</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>-7170000000</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>-5571000000</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -3832,34 +4212,34 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>90000000000</v>
+        <v>128249000000</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>97200000000</v>
+        <v>134047000000</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>104976000000</v>
+        <v>107147000000</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>113374080000</v>
+        <v>90488000000</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>122444006400</v>
+        <v>65339000000</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>132239526912</v>
+        <v>63090000000</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>142818689064.96</v>
+        <v>50672000000</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>154244184190.16</v>
+        <v>62146000000</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>166583718925.37</v>
+        <v>56950000000</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>179910416439.4</v>
+        <v>73733000000</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -3869,34 +4249,34 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>350000000000</v>
+        <v>321686000000</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>371000000000</v>
+        <v>375319000000</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>393260000000</v>
+        <v>365725000000</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>416855600000</v>
+        <v>338516000000</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>441866936000</v>
+        <v>323888000000</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>468378952160</v>
+        <v>351002000000</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>496481689289.6</v>
+        <v>352755000000</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>526270590646.98</v>
+        <v>352583000000</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>557846826085.79</v>
+        <v>364980000000</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>591317635650.9399</v>
+        <v>359241000000</v>
       </c>
     </row>
   </sheetData>
@@ -3947,34 +4327,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -4001,34 +4381,34 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>38000000000</v>
+        <v>45687000000</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>41800000000</v>
+        <v>48351000000</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>45980000000</v>
+        <v>59531000000</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>50578000000</v>
+        <v>55256000000</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>55635800000</v>
+        <v>57411000000</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>61199380000</v>
+        <v>94680000000</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>67319318000</v>
+        <v>99803000000</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>74051249800</v>
+        <v>96995000000</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>81456374780</v>
+        <v>93736000000</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>89602012258</v>
+        <v>112010000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -4038,34 +4418,34 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>11000000000</v>
+        <v>10505000000</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>11550000000</v>
+        <v>10157000000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>12127500000</v>
+        <v>10903000000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>12733875000</v>
+        <v>12547000000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>13370568750</v>
+        <v>11056000000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>14039097187.5</v>
+        <v>11284000000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>14741052046.88</v>
+        <v>11104000000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>15478104649.22</v>
+        <v>11519000000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>16252009881.68</v>
+        <v>11520000000</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>17064610375.76</v>
+        <v>11950000000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -4075,34 +4455,34 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>8000000000</v>
+        <v>4210000000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8640000000</v>
+        <v>4840000000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9331200000</v>
+        <v>5340000000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10077696000</v>
+        <v>6068000000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>10883911680</v>
+        <v>6829000000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>11754624614.4</v>
+        <v>7906000000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>12694994583.55</v>
+        <v>9038000000</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13710594150.24</v>
+        <v>10833000000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>14807441682.26</v>
+        <v>11640000000</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>15992037016.84</v>
+        <v>12800000000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4111,16 +4491,36 @@
           <t xml:space="preserve">    Deferred Income Taxes</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>4938000000</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>5966000000</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>-32590000000</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-340000000</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>-4774000000</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>895000000</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>-222000000</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>-1071000000</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>-1850000000</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -4128,16 +4528,36 @@
           <t xml:space="preserve">    Change in Accounts Receivable</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>527000000</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>-2093000000</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>-5322000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>245000000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6917000000</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>-10125000000</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>-1823000000</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>-1688000000</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>-3900000000</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>-4200000000</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -4145,16 +4565,36 @@
           <t xml:space="preserve">    Change in Inventories</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>217000000</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>-2723000000</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>828000000</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-289000000</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>-127000000</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>-2642000000</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1484000000</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>-1618000000</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>-955000000</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>613000000</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -4162,16 +4602,36 @@
           <t xml:space="preserve">    Change in Accounts Payable</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>2172000000</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>8966000000</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>9175000000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>-1923000000</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>-4062000000</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>12326000000</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>9448000000</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>-1886000000</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>6350000000</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>5200000000</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -4180,34 +4640,34 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>70000000000</v>
+        <v>65824000000</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>76300000000</v>
+        <v>63598000000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>83167000000</v>
+        <v>77434000000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>90652030000</v>
+        <v>69391000000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>98810712700</v>
+        <v>80674000000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>107703676843</v>
+        <v>104038000000</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>117397007758.87</v>
+        <v>122151000000</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>127962738457.17</v>
+        <v>110543000000</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>139479384918.31</v>
+        <v>118260000000</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>152032529560.96</v>
+        <v>111482000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -4234,34 +4694,34 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>12000000000</v>
+        <v>-12734000000</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>12720000000</v>
+        <v>-12451000000</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>13483200000</v>
+        <v>-13313000000</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>14292192000</v>
+        <v>-10495000000</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>15149723520</v>
+        <v>-7309000000</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>16058706931.2</v>
+        <v>-11085000000</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>17022229347.07</v>
+        <v>-10708000000</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>18043563107.9</v>
+        <v>-10959000000</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>19126176894.37</v>
+        <v>-9447000000</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>20273747508.03</v>
+        <v>-12715000000</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -4270,16 +4730,36 @@
           <t xml:space="preserve">    Purchases of Marketable Securities</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>-142428000000</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>-159486000000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>-71356000000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>-39630000000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>-114938000000</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>-109558000000</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>-76923000000</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>-29514000000</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>-48660000000</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>-38500000000</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -4287,16 +4767,36 @@
           <t xml:space="preserve">    Proceeds from Sales/Maturities of Marketable Securities</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>119937000000</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>146194000000</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>88206000000</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>98724000000</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>120541000000</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>106877000000</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>98844000000</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>43900000000</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>61760000000</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>56200000000</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -4304,16 +4804,36 @@
           <t xml:space="preserve">    Payments for Business Acquisitions, Net</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>-297000000</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>-329000000</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>-721000000</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>-624000000</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>-1524000000</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>-33000000</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>-306000000</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -4322,34 +4842,34 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>-15000000000</v>
+        <v>-45977000000</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>-15750000000</v>
+        <v>-46446000000</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>-16537500000</v>
+        <v>16066000000</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>-17364375000</v>
+        <v>45896000000</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-18232593750</v>
+        <v>-4289000000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>-19144223437.5</v>
+        <v>-14545000000</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>-20101434609.38</v>
+        <v>-22354000000</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>-21106506339.84</v>
+        <v>3705000000</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-22161831656.84</v>
+        <v>2490000000</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>-23269923239.68</v>
+        <v>4985000000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -4376,34 +4896,34 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>45000000000</v>
+        <v>-29722000000</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>48150000000</v>
+        <v>-32900000000</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>51520500000</v>
+        <v>-72738000000</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>55126935000</v>
+        <v>-66897000000</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>58985820450</v>
+        <v>-72358000000</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>63114827881.5</v>
+        <v>-85971000000</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>67532865833.21</v>
+        <v>-89402000000</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>72260166441.53</v>
+        <v>-77550000000</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>77318378092.44</v>
+        <v>-94949000000</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>82730664558.91</v>
+        <v>-90711000000</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -4413,34 +4933,34 @@
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>14000000000</v>
+        <v>-12150000000</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>14560000000</v>
+        <v>-12769000000</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>15142400000</v>
+        <v>-13712000000</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>15748096000</v>
+        <v>-14119000000</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>16378019840</v>
+        <v>-14081000000</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>17033140633.6</v>
+        <v>-14467000000</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>17714466258.94</v>
+        <v>-14841000000</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>18423044909.3</v>
+        <v>-15025000000</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>19159966705.67</v>
+        <v>-15234000000</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>19926365373.9</v>
+        <v>-15421000000</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -4449,16 +4969,36 @@
           <t xml:space="preserve">    Proceeds from Issuance of Common Stock</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>495000000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>555000000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>569000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>781000000</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>880000000</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>1105000000</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1210000000</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>1285000000</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>1420000000</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -4466,16 +5006,36 @@
           <t xml:space="preserve">    Proceeds from Issuance of Long-Term Debt</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>24954000000</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>28662000000</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>6969000000</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>6963000000</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>16091000000</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>20393000000</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>5465000000</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>5228000000</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>5200000000</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -4483,16 +5043,36 @@
           <t xml:space="preserve">    Repayments of Long-Term Debt</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>-2500000000</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-3500000000</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>-6500000000</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-8805000000</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>-12629000000</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>-11135000000</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>-9543000000</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>-11151000000</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>-10800000000</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>-11250000000</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -4501,34 +5081,34 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>-50000000000</v>
+        <v>-20483000000</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-53000000000</v>
+        <v>-17347000000</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-56180000000</v>
+        <v>-86820000000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-59550800000</v>
+        <v>-90976000000</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-63123848000</v>
+        <v>-86896000000</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-66911278880</v>
+        <v>-93353000000</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-70925955612.8</v>
+        <v>-110749000000</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-75181512949.57001</v>
+        <v>-108488000000</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>-79692403726.53999</v>
+        <v>-120220000000</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>-84473947950.13</v>
+        <v>-110762000000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -4554,16 +5134,36 @@
           <t xml:space="preserve">    Net Increase / (Decrease) in Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="B27" s="7" t="n">
+        <v>-636000000</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>-195000000</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>6680000000</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>24311000000</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>-10433000000</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>-3860000000</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>-10952000000</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>5760000000</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>5705000000</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -4572,34 +5172,34 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>30000000000</v>
+        <v>21120000000</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>31200000000</v>
+        <v>20484000000</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>32448000000</v>
+        <v>20289000000</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>33745920000</v>
+        <v>25913000000</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>35095756800</v>
+        <v>50224000000</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>36499587072</v>
+        <v>39789000000</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>37959570554.88</v>
+        <v>35929000000</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>39477953377.08</v>
+        <v>24977000000</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>41057071512.16</v>
+        <v>30737000000</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>42699354372.64</v>
+        <v>31267000000</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -4609,34 +5209,34 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>30000000000</v>
+        <v>20484000000</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>31200000000</v>
+        <v>20289000000</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>32448000000</v>
+        <v>26969000000</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>33745920000</v>
+        <v>50224000000</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>35095756800</v>
+        <v>39789000000</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>36499587072</v>
+        <v>35929000000</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>37959570554.88</v>
+        <v>24977000000</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>39477953377.08</v>
+        <v>30737000000</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>41057071512.16</v>
+        <v>31267000000</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>42699354372.64</v>
+        <v>36972000000</v>
       </c>
     </row>
   </sheetData>
@@ -4645,510 +5245,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AAPL — LOUGHRAN-MCDONALD FINANCIAL SENTIMENT ANALYSIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Item 7 (MD&amp;A) Natural Language Processing — Loughran-McDonald Lexicon (2011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Fiscal Year</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Total Words</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Positive Count</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Negative Count</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Net Score</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>P/N Ratio</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>Net Sentiment %</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Uncertainty Count</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Litigious Count</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>Strong Modal</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
-        <is>
-          <t>Weak Modal</t>
-        </is>
-      </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>Tone Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="21" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B4" s="22" t="n">
-        <v>5068</v>
-      </c>
-      <c r="C4" s="22" t="n">
-        <v>132</v>
-      </c>
-      <c r="D4" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="E4" s="22" t="n">
-        <v>-44</v>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G4" s="24" t="n">
-        <v>-0.008682</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>126</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="26" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B5" s="27" t="n">
-        <v>5234</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>120</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>179</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-59</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>0.6704</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>-0.011272</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>130</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="K5" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="L5" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="21" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <v>5031</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>127</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>142</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>-15</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>0.8944</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>-0.002982</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>120</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>54</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="L6" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="26" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B7" s="27" t="n">
-        <v>2962</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>57</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>0.6196</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>-0.011816</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>64</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="L7" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>2784</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>51</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>96</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>-45</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>0.5312</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>-0.016164</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="26" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="27" t="n">
-        <v>1626</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>1.5806</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>0.01107</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="21" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>1542</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>39</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.002594</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="26" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B11" s="27" t="n">
-        <v>1358</v>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>24</v>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>46</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>-22</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>0.5217000000000001</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>-0.0162</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>1338</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>0.7647</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.005979</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B13" s="27" t="n">
-        <v>1569</v>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>32</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>37</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>0.8649</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>-0.003187</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="25" t="inlineStr">
-        <is>
-          <t>Cautious / Negative</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5522,4 +5618,544 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AAPL — LOUGHRAN-MCDONALD FINANCIAL SENTIMENT ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Item 7 (MD&amp;A) Natural Language Processing — Loughran-McDonald Lexicon (2011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Raw MD&amp;A Words</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Cleaned MD&amp;A Words</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Positive Count</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Negative Count</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Net Score</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>P/N Ratio</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Net Sentiment %</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Uncertainty Count</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Litigious Count</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>Strong Modal</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Weak Modal</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
+        <is>
+          <t>Tone Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="22" t="n">
+        <v>9194</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>5068</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>132</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>176</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>9411</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>5234</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>179</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="L5" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="M5" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>8955</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>5031</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>127</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>142</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>120</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="26" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>5249</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>2962</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>64</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>4923</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>2784</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>96</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>2925</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>1.5806</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>1542</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>2487</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>1358</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>2441</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>1338</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>2805</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>0.8649</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>Cautious / Negative</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>